--- a/tools/importer/reports/import-savings-program-landing.report.xlsx
+++ b/tools/importer/reports/import-savings-program-landing.report.xlsx
@@ -52,7 +52,7 @@
     <t>savings-program-landing</t>
   </si>
   <si>
-    <t>2026-05-25T05:32:01.323Z</t>
+    <t>2026-05-25T06:07:08.514Z</t>
   </si>
   <si>
     <t>Durysta Home</t>
